--- a/data/nzd0273/nzd0273.xlsx
+++ b/data/nzd0273/nzd0273.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R360"/>
+  <dimension ref="A1:R362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21940,7 +21940,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>351.27</v>
+        <v>335.81</v>
       </c>
       <c r="C359" t="n">
         <v>329.24</v>
@@ -22000,7 +22000,7 @@
         </is>
       </c>
       <c r="B360" t="n">
-        <v>362.9</v>
+        <v>336.19</v>
       </c>
       <c r="C360" t="n">
         <v>327.23</v>
@@ -22048,6 +22048,126 @@
         <v>323.94</v>
       </c>
       <c r="R360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>334.86</v>
+      </c>
+      <c r="C361" t="n">
+        <v>331.27</v>
+      </c>
+      <c r="D361" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="E361" t="n">
+        <v>327.43</v>
+      </c>
+      <c r="F361" t="n">
+        <v>335.62</v>
+      </c>
+      <c r="G361" t="n">
+        <v>338.55</v>
+      </c>
+      <c r="H361" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="I361" t="n">
+        <v>331.05</v>
+      </c>
+      <c r="J361" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="K361" t="n">
+        <v>325.18</v>
+      </c>
+      <c r="L361" t="n">
+        <v>323.18</v>
+      </c>
+      <c r="M361" t="n">
+        <v>317.27</v>
+      </c>
+      <c r="N361" t="n">
+        <v>325.88</v>
+      </c>
+      <c r="O361" t="n">
+        <v>314.41</v>
+      </c>
+      <c r="P361" t="n">
+        <v>319.94</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>321.92</v>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>334.29</v>
+      </c>
+      <c r="C362" t="n">
+        <v>330.33</v>
+      </c>
+      <c r="D362" t="n">
+        <v>334.31</v>
+      </c>
+      <c r="E362" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="F362" t="n">
+        <v>335.65</v>
+      </c>
+      <c r="G362" t="n">
+        <v>338.3</v>
+      </c>
+      <c r="H362" t="n">
+        <v>329.74</v>
+      </c>
+      <c r="I362" t="n">
+        <v>330.45</v>
+      </c>
+      <c r="J362" t="n">
+        <v>325.52</v>
+      </c>
+      <c r="K362" t="n">
+        <v>324.92</v>
+      </c>
+      <c r="L362" t="n">
+        <v>322.76</v>
+      </c>
+      <c r="M362" t="n">
+        <v>316.1</v>
+      </c>
+      <c r="N362" t="n">
+        <v>324.69</v>
+      </c>
+      <c r="O362" t="n">
+        <v>313.26</v>
+      </c>
+      <c r="P362" t="n">
+        <v>319.46</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="R362" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22064,7 +22184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B379"/>
+  <dimension ref="A1:B381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25857,6 +25977,26 @@
       </c>
       <c r="B379" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>
@@ -26025,28 +26165,28 @@
         <v>0.1874</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.603489695702075</v>
+        <v>-0.6222605479032977</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K2" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06269743157590091</v>
+        <v>0.06786414953023046</v>
       </c>
       <c r="M2" t="n">
-        <v>9.588444386721173</v>
+        <v>9.376965430472371</v>
       </c>
       <c r="N2" t="n">
-        <v>306.7150524722966</v>
+        <v>301.3214339988025</v>
       </c>
       <c r="O2" t="n">
-        <v>17.51328217303361</v>
+        <v>17.35861267494619</v>
       </c>
       <c r="P2" t="n">
-        <v>347.6817004534167</v>
+        <v>347.8801136390564</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26103,28 +26243,28 @@
         <v>0.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3359100919650235</v>
+        <v>-0.324884103383786</v>
       </c>
       <c r="J3" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K3" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2213969208402825</v>
+        <v>0.2075066452393211</v>
       </c>
       <c r="M3" t="n">
-        <v>3.665623138026427</v>
+        <v>3.702098019123116</v>
       </c>
       <c r="N3" t="n">
-        <v>22.640934568542</v>
+        <v>23.1314613422925</v>
       </c>
       <c r="O3" t="n">
-        <v>4.758249107449294</v>
+        <v>4.809517786877652</v>
       </c>
       <c r="P3" t="n">
-        <v>329.1286953070436</v>
+        <v>329.0124463204857</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26181,28 +26321,28 @@
         <v>0.1113</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3031665088732148</v>
+        <v>-0.2940402446644082</v>
       </c>
       <c r="J4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K4" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1827882713643664</v>
+        <v>0.172878510212754</v>
       </c>
       <c r="M4" t="n">
-        <v>3.490461619665354</v>
+        <v>3.520935748345253</v>
       </c>
       <c r="N4" t="n">
-        <v>23.3872720874355</v>
+        <v>23.67899105214524</v>
       </c>
       <c r="O4" t="n">
-        <v>4.836038883987131</v>
+        <v>4.866106354380804</v>
       </c>
       <c r="P4" t="n">
-        <v>334.0986315708255</v>
+        <v>334.0023265269281</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26259,28 +26399,28 @@
         <v>0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6814759742284702</v>
+        <v>-0.6757378082808135</v>
       </c>
       <c r="J5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K5" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5125010697180374</v>
+        <v>0.5094418840374523</v>
       </c>
       <c r="M5" t="n">
-        <v>3.948282223014691</v>
+        <v>3.956649445219262</v>
       </c>
       <c r="N5" t="n">
-        <v>25.14263825460294</v>
+        <v>25.16944298251445</v>
       </c>
       <c r="O5" t="n">
-        <v>5.01424353762389</v>
+        <v>5.016915684214202</v>
       </c>
       <c r="P5" t="n">
-        <v>339.91852144867</v>
+        <v>339.8579683375257</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26337,28 +26477,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5173171233668182</v>
+        <v>-0.5142463388518966</v>
       </c>
       <c r="J6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K6" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5337707751574994</v>
+        <v>0.5327243861411122</v>
       </c>
       <c r="M6" t="n">
-        <v>2.74866454649713</v>
+        <v>2.748473849336864</v>
       </c>
       <c r="N6" t="n">
-        <v>13.30421537788845</v>
+        <v>13.27805016997156</v>
       </c>
       <c r="O6" t="n">
-        <v>3.647494397238801</v>
+        <v>3.643905894774391</v>
       </c>
       <c r="P6" t="n">
-        <v>346.45445860949</v>
+        <v>346.4220530662177</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26415,28 +26555,28 @@
         <v>0.1226</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5358543644662619</v>
+        <v>-0.5358505454946071</v>
       </c>
       <c r="J7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K7" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5689411462695815</v>
+        <v>0.5717027821195309</v>
       </c>
       <c r="M7" t="n">
-        <v>2.721610954343108</v>
+        <v>2.707192678494744</v>
       </c>
       <c r="N7" t="n">
-        <v>12.38208065654964</v>
+        <v>12.31356057824565</v>
       </c>
       <c r="O7" t="n">
-        <v>3.518818076648698</v>
+        <v>3.509068334792819</v>
       </c>
       <c r="P7" t="n">
-        <v>352.6871809175264</v>
+        <v>352.6871412895901</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26493,28 +26633,28 @@
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4194545507502269</v>
+        <v>-0.4214612543588835</v>
       </c>
       <c r="J8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K8" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4025358067597676</v>
+        <v>0.4072188397728279</v>
       </c>
       <c r="M8" t="n">
-        <v>2.904098501491807</v>
+        <v>2.898731990534776</v>
       </c>
       <c r="N8" t="n">
-        <v>14.86305357069395</v>
+        <v>14.80141345979867</v>
       </c>
       <c r="O8" t="n">
-        <v>3.855263100061259</v>
+        <v>3.84726051363807</v>
       </c>
       <c r="P8" t="n">
-        <v>342.570605397806</v>
+        <v>342.5917802671441</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26571,28 +26711,28 @@
         <v>0.1214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6241809780318581</v>
+        <v>-0.6163067906093612</v>
       </c>
       <c r="J9" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K9" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5473905222833955</v>
+        <v>0.5396679496113159</v>
       </c>
       <c r="M9" t="n">
-        <v>3.398881052543731</v>
+        <v>3.417472142187459</v>
       </c>
       <c r="N9" t="n">
-        <v>18.33488907085117</v>
+        <v>18.54640939221335</v>
       </c>
       <c r="O9" t="n">
-        <v>4.281925860036716</v>
+        <v>4.306554236534511</v>
       </c>
       <c r="P9" t="n">
-        <v>339.7921828370912</v>
+        <v>339.709089626151</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26649,28 +26789,28 @@
         <v>0.1419</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4503008948440292</v>
+        <v>-0.4462174465823455</v>
       </c>
       <c r="J10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L10" t="n">
-        <v>0.403929716573398</v>
+        <v>0.4010673309518779</v>
       </c>
       <c r="M10" t="n">
-        <v>3.137242978669103</v>
+        <v>3.139668334343924</v>
       </c>
       <c r="N10" t="n">
-        <v>17.03052922403556</v>
+        <v>17.02061143780906</v>
       </c>
       <c r="O10" t="n">
-        <v>4.126806177182975</v>
+        <v>4.125604372429458</v>
       </c>
       <c r="P10" t="n">
-        <v>333.836098449008</v>
+        <v>333.7930079921388</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26727,28 +26867,28 @@
         <v>0.1644</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.247889197433701</v>
+        <v>-0.2439457718392771</v>
       </c>
       <c r="J11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K11" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2621322627700048</v>
+        <v>0.2566062390242586</v>
       </c>
       <c r="M11" t="n">
-        <v>2.228678593494287</v>
+        <v>2.234816472537297</v>
       </c>
       <c r="N11" t="n">
-        <v>9.84473670700347</v>
+        <v>9.868693026093847</v>
       </c>
       <c r="O11" t="n">
-        <v>3.137632340954477</v>
+        <v>3.141447600405559</v>
       </c>
       <c r="P11" t="n">
-        <v>327.8564561591189</v>
+        <v>327.8148426322884</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26805,28 +26945,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09267575521836896</v>
+        <v>-0.09050540906692627</v>
       </c>
       <c r="J12" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K12" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04118488033859335</v>
+        <v>0.03970171806578404</v>
       </c>
       <c r="M12" t="n">
-        <v>2.520636816547212</v>
+        <v>2.516732444254457</v>
       </c>
       <c r="N12" t="n">
-        <v>11.38046980047795</v>
+        <v>11.34141576373754</v>
       </c>
       <c r="O12" t="n">
-        <v>3.373495190522428</v>
+        <v>3.367701851966344</v>
       </c>
       <c r="P12" t="n">
-        <v>323.3450820766225</v>
+        <v>323.3221799893038</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26883,28 +27023,28 @@
         <v>0.1181</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2693977505442447</v>
+        <v>-0.263167407253308</v>
       </c>
       <c r="J13" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K13" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2390156519756654</v>
+        <v>0.2299509261826765</v>
       </c>
       <c r="M13" t="n">
-        <v>2.64484386491601</v>
+        <v>2.667105235231518</v>
       </c>
       <c r="N13" t="n">
-        <v>13.15128442390076</v>
+        <v>13.27604734712584</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6264699673237</v>
+        <v>3.643631066275212</v>
       </c>
       <c r="P13" t="n">
-        <v>317.8594015213267</v>
+        <v>317.7936571305252</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26961,28 +27101,28 @@
         <v>0.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.344742238168545</v>
+        <v>-0.3355425949344371</v>
       </c>
       <c r="J14" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K14" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3622252136566235</v>
+        <v>0.3443247786049896</v>
       </c>
       <c r="M14" t="n">
-        <v>2.718236235905163</v>
+        <v>2.746861827707475</v>
       </c>
       <c r="N14" t="n">
-        <v>11.90991110988523</v>
+        <v>12.27261645023423</v>
       </c>
       <c r="O14" t="n">
-        <v>3.451073906755001</v>
+        <v>3.503229431572278</v>
       </c>
       <c r="P14" t="n">
-        <v>325.6115313222757</v>
+        <v>325.5144524973416</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27039,28 +27179,28 @@
         <v>0.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3519543508743955</v>
+        <v>-0.3401071124835452</v>
       </c>
       <c r="J15" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K15" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L15" t="n">
-        <v>0.179926927006686</v>
+        <v>0.1685421287813501</v>
       </c>
       <c r="M15" t="n">
-        <v>4.359043557405016</v>
+        <v>4.405342893548832</v>
       </c>
       <c r="N15" t="n">
-        <v>32.13363999779364</v>
+        <v>32.665142095896</v>
       </c>
       <c r="O15" t="n">
-        <v>5.668654161068008</v>
+        <v>5.715342692778448</v>
       </c>
       <c r="P15" t="n">
-        <v>311.8074578944625</v>
+        <v>311.6824393799132</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27117,28 +27257,28 @@
         <v>0.1368</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3381193088124473</v>
+        <v>-0.3290413603957809</v>
       </c>
       <c r="J16" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K16" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L16" t="n">
-        <v>0.206610251527458</v>
+        <v>0.1969896817033172</v>
       </c>
       <c r="M16" t="n">
-        <v>3.888345848324843</v>
+        <v>3.918077981287036</v>
       </c>
       <c r="N16" t="n">
-        <v>24.98650544216504</v>
+        <v>25.26387598198838</v>
       </c>
       <c r="O16" t="n">
-        <v>4.998650362064248</v>
+        <v>5.026318332735043</v>
       </c>
       <c r="P16" t="n">
-        <v>319.9658614450741</v>
+        <v>319.8700648203491</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27195,28 +27335,28 @@
         <v>0.1222</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3797916120003907</v>
+        <v>-0.371117674735608</v>
       </c>
       <c r="J17" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K17" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2173650714695234</v>
+        <v>0.2093525521666645</v>
       </c>
       <c r="M17" t="n">
-        <v>4.238901197409986</v>
+        <v>4.264140754210759</v>
       </c>
       <c r="N17" t="n">
-        <v>29.55909023230076</v>
+        <v>29.77482652724945</v>
       </c>
       <c r="O17" t="n">
-        <v>5.43682722111902</v>
+        <v>5.456631426736594</v>
       </c>
       <c r="P17" t="n">
-        <v>323.5128424848629</v>
+        <v>323.4213089747367</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27254,7 +27394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R360"/>
+  <dimension ref="A1:R362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60181,7 +60321,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>-38.79514219606952,174.59146127535314</t>
+          <t>-38.79517275778865,174.5916349230555</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -60273,7 +60413,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>-38.79511920541895,174.59133064654637</t>
+          <t>-38.79517200659817,174.59163065486968</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -60352,6 +60492,190 @@
         </is>
       </c>
       <c r="R360" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>-38.79517463576416,174.59164559352044</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>-38.79450050924937,174.59189333126423</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>-38.79381131299196,174.59205548147878</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-38.79314563398308,174.59235129044416</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>-38.79244820140807,174.59246671741766</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>-38.79175880610375,174.59264203004503</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-38.79108590332257,174.59292855717882</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>-38.79039574581634,174.59308407265047</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>-38.789717488867105,174.59331694353727</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>-38.78903232313794,174.59350286119076</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>-38.788349046752906,174.59370167624388</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>-38.787693526001746,174.59393811054312</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>-38.787030622980154,174.59411909604435</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>-38.78640880952183,174.5945473804466</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>-38.78573381318918,174.59479221410174</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>-38.78506930912409,174.5950756487594</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>-38.795175762549,174.59165199579962</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>-38.79450236744146,174.59190388931287</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>-38.79381327001724,174.59206660102004</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-38.79314616771198,174.59235432301935</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>-38.792448142104924,174.59246638046815</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>-38.79175926600192,174.59264484742718</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>-38.791085011561954,174.5929225631898</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>-38.790396743718766,174.59309086104264</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>-38.78971835370815,174.5933228267562</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>-38.78903275555583,174.5935058027725</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>-38.78834974526922,174.5937064279853</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>-38.787696118827185,174.59395116509182</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>-38.78703402574882,174.59413208624017</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>-38.78641221037321,174.59455988487815</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>-38.7857352326697,174.5947974332954</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>-38.78507034415675,174.59507945438813</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0273/nzd0273.xlsx
+++ b/data/nzd0273/nzd0273.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R362"/>
+  <dimension ref="A1:R364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22168,6 +22168,126 @@
         <v>321.57</v>
       </c>
       <c r="R362" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>334.29</v>
+      </c>
+      <c r="C363" t="n">
+        <v>332.35</v>
+      </c>
+      <c r="D363" t="n">
+        <v>336.61</v>
+      </c>
+      <c r="E363" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="F363" t="n">
+        <v>335.02</v>
+      </c>
+      <c r="G363" t="n">
+        <v>339.65</v>
+      </c>
+      <c r="H363" t="n">
+        <v>329.3</v>
+      </c>
+      <c r="I363" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="J363" t="n">
+        <v>326.64</v>
+      </c>
+      <c r="K363" t="n">
+        <v>325.13</v>
+      </c>
+      <c r="L363" t="n">
+        <v>323.3</v>
+      </c>
+      <c r="M363" t="n">
+        <v>317.03</v>
+      </c>
+      <c r="N363" t="n">
+        <v>326.01</v>
+      </c>
+      <c r="O363" t="n">
+        <v>311.48</v>
+      </c>
+      <c r="P363" t="n">
+        <v>320.26</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>321.57</v>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>334.29</v>
+      </c>
+      <c r="C364" t="n">
+        <v>329.53</v>
+      </c>
+      <c r="D364" t="n">
+        <v>334.22</v>
+      </c>
+      <c r="E364" t="n">
+        <v>323.59</v>
+      </c>
+      <c r="F364" t="n">
+        <v>333.27</v>
+      </c>
+      <c r="G364" t="n">
+        <v>336.44</v>
+      </c>
+      <c r="H364" t="n">
+        <v>325.23</v>
+      </c>
+      <c r="I364" t="n">
+        <v>328.2</v>
+      </c>
+      <c r="J364" t="n">
+        <v>324.83</v>
+      </c>
+      <c r="K364" t="n">
+        <v>323.7</v>
+      </c>
+      <c r="L364" t="n">
+        <v>322</v>
+      </c>
+      <c r="M364" t="n">
+        <v>314.72</v>
+      </c>
+      <c r="N364" t="n">
+        <v>324.59</v>
+      </c>
+      <c r="O364" t="n">
+        <v>308.46</v>
+      </c>
+      <c r="P364" t="n">
+        <v>315.66</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>316.18</v>
+      </c>
+      <c r="R364" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -22184,7 +22304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B381"/>
+  <dimension ref="A1:B383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25997,6 +26117,26 @@
       </c>
       <c r="B381" t="n">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
@@ -26165,28 +26305,28 @@
         <v>0.1874</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6222605479032977</v>
+        <v>-0.6191142004081397</v>
       </c>
       <c r="J2" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K2" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06786414953023046</v>
+        <v>0.06792185424370101</v>
       </c>
       <c r="M2" t="n">
-        <v>9.376965430472371</v>
+        <v>9.34983916700733</v>
       </c>
       <c r="N2" t="n">
-        <v>301.3214339988025</v>
+        <v>299.692766141468</v>
       </c>
       <c r="O2" t="n">
-        <v>17.35861267494619</v>
+        <v>17.31163672624481</v>
       </c>
       <c r="P2" t="n">
-        <v>347.8801136390564</v>
+        <v>347.8464842325619</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26243,28 +26383,28 @@
         <v>0.1848</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.324884103383786</v>
+        <v>-0.3139889599805198</v>
       </c>
       <c r="J3" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K3" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2075066452393211</v>
+        <v>0.1940771981907136</v>
       </c>
       <c r="M3" t="n">
-        <v>3.702098019123116</v>
+        <v>3.740681435116092</v>
       </c>
       <c r="N3" t="n">
-        <v>23.1314613422925</v>
+        <v>23.6250712670417</v>
       </c>
       <c r="O3" t="n">
-        <v>4.809517786877652</v>
+        <v>4.86056285496255</v>
       </c>
       <c r="P3" t="n">
-        <v>329.0124463204857</v>
+        <v>328.8972434551394</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26321,28 +26461,28 @@
         <v>0.1113</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2940402446644082</v>
+        <v>-0.2845200594308249</v>
       </c>
       <c r="J4" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K4" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L4" t="n">
-        <v>0.172878510212754</v>
+        <v>0.162482698426814</v>
       </c>
       <c r="M4" t="n">
-        <v>3.520935748345253</v>
+        <v>3.555685056356652</v>
       </c>
       <c r="N4" t="n">
-        <v>23.67899105214524</v>
+        <v>24.02084661864837</v>
       </c>
       <c r="O4" t="n">
-        <v>4.866106354380804</v>
+        <v>4.901106672849345</v>
       </c>
       <c r="P4" t="n">
-        <v>334.0023265269281</v>
+        <v>333.9015731495447</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26399,28 +26539,28 @@
         <v>0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6757378082808135</v>
+        <v>-0.6720900297839187</v>
       </c>
       <c r="J5" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K5" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5094418840374523</v>
+        <v>0.5086772245872913</v>
       </c>
       <c r="M5" t="n">
-        <v>3.956649445219262</v>
+        <v>3.95420215790696</v>
       </c>
       <c r="N5" t="n">
-        <v>25.16944298251445</v>
+        <v>25.11628330735872</v>
       </c>
       <c r="O5" t="n">
-        <v>5.016915684214202</v>
+        <v>5.011614840284389</v>
       </c>
       <c r="P5" t="n">
-        <v>339.8579683375257</v>
+        <v>339.8193854929199</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26477,28 +26617,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5142463388518966</v>
+        <v>-0.5127588937177702</v>
       </c>
       <c r="J6" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K6" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5327243861411122</v>
+        <v>0.5337739739978296</v>
       </c>
       <c r="M6" t="n">
-        <v>2.748473849336864</v>
+        <v>2.740550194861186</v>
       </c>
       <c r="N6" t="n">
-        <v>13.27805016997156</v>
+        <v>13.2203023234214</v>
       </c>
       <c r="O6" t="n">
-        <v>3.643905894774391</v>
+        <v>3.63597336670958</v>
       </c>
       <c r="P6" t="n">
-        <v>346.4220530662177</v>
+        <v>346.4063225378671</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26555,28 +26695,28 @@
         <v>0.1226</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5358505454946071</v>
+        <v>-0.536203742973519</v>
       </c>
       <c r="J7" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K7" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5717027821195309</v>
+        <v>0.574470905819634</v>
       </c>
       <c r="M7" t="n">
-        <v>2.707192678494744</v>
+        <v>2.70103905499752</v>
       </c>
       <c r="N7" t="n">
-        <v>12.31356057824565</v>
+        <v>12.26017775454058</v>
       </c>
       <c r="O7" t="n">
-        <v>3.509068334792819</v>
+        <v>3.501453663057756</v>
       </c>
       <c r="P7" t="n">
-        <v>352.6871412895901</v>
+        <v>352.6909066610974</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26633,28 +26773,28 @@
         <v>0.149</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4214612543588835</v>
+        <v>-0.4256620060507809</v>
       </c>
       <c r="J8" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K8" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4072188397728279</v>
+        <v>0.4128784403967638</v>
       </c>
       <c r="M8" t="n">
-        <v>2.898731990534776</v>
+        <v>2.904981900387291</v>
       </c>
       <c r="N8" t="n">
-        <v>14.80141345979867</v>
+        <v>14.83240111769765</v>
       </c>
       <c r="O8" t="n">
-        <v>3.84726051363807</v>
+        <v>3.851285644781188</v>
       </c>
       <c r="P8" t="n">
-        <v>342.5917802671441</v>
+        <v>342.6362801619234</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26711,28 +26851,28 @@
         <v>0.1214</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6163067906093612</v>
+        <v>-0.6104575516111544</v>
       </c>
       <c r="J9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5396679496113159</v>
+        <v>0.5353131224089143</v>
       </c>
       <c r="M9" t="n">
-        <v>3.417472142187459</v>
+        <v>3.42611688881992</v>
       </c>
       <c r="N9" t="n">
-        <v>18.54640939221335</v>
+        <v>18.6225575045364</v>
       </c>
       <c r="O9" t="n">
-        <v>4.306554236534511</v>
+        <v>4.315386136203387</v>
       </c>
       <c r="P9" t="n">
-        <v>339.709089626151</v>
+        <v>339.6471864305999</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26789,28 +26929,28 @@
         <v>0.1419</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4462174465823455</v>
+        <v>-0.4422600262190597</v>
       </c>
       <c r="J10" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K10" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4010673309518779</v>
+        <v>0.398276191408898</v>
       </c>
       <c r="M10" t="n">
-        <v>3.139668334343924</v>
+        <v>3.141347291277615</v>
       </c>
       <c r="N10" t="n">
-        <v>17.02061143780906</v>
+        <v>17.01155795265552</v>
       </c>
       <c r="O10" t="n">
-        <v>4.125604372429458</v>
+        <v>4.124506995103236</v>
       </c>
       <c r="P10" t="n">
-        <v>333.7930079921388</v>
+        <v>333.7511328392299</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26867,28 +27007,28 @@
         <v>0.1644</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2439457718392771</v>
+        <v>-0.2407459661925977</v>
       </c>
       <c r="J11" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K11" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2566062390242586</v>
+        <v>0.252650007023926</v>
       </c>
       <c r="M11" t="n">
-        <v>2.234816472537297</v>
+        <v>2.237716213974782</v>
       </c>
       <c r="N11" t="n">
-        <v>9.868693026093847</v>
+        <v>9.869578879052295</v>
       </c>
       <c r="O11" t="n">
-        <v>3.141447600405559</v>
+        <v>3.141588591628811</v>
       </c>
       <c r="P11" t="n">
-        <v>327.8148426322884</v>
+        <v>327.7809838471458</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26945,28 +27085,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09050540906692627</v>
+        <v>-0.08871186153646932</v>
       </c>
       <c r="J12" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K12" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03970171806578404</v>
+        <v>0.03855427081578133</v>
       </c>
       <c r="M12" t="n">
-        <v>2.516732444254457</v>
+        <v>2.511209268235356</v>
       </c>
       <c r="N12" t="n">
-        <v>11.34141576373754</v>
+        <v>11.29773881307633</v>
       </c>
       <c r="O12" t="n">
-        <v>3.367701851966344</v>
+        <v>3.361210914696716</v>
       </c>
       <c r="P12" t="n">
-        <v>323.3221799893038</v>
+        <v>323.3032057552687</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -27023,28 +27163,28 @@
         <v>0.1181</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.263167407253308</v>
+        <v>-0.2579210117171163</v>
       </c>
       <c r="J13" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K13" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2299509261826765</v>
+        <v>0.2228965496303462</v>
       </c>
       <c r="M13" t="n">
-        <v>2.667105235231518</v>
+        <v>2.683433195754804</v>
       </c>
       <c r="N13" t="n">
-        <v>13.27604734712584</v>
+        <v>13.35133838006234</v>
       </c>
       <c r="O13" t="n">
-        <v>3.643631066275212</v>
+        <v>3.65394832750305</v>
       </c>
       <c r="P13" t="n">
-        <v>317.7936571305252</v>
+        <v>317.738142178584</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27101,28 +27241,28 @@
         <v>0.1197</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3355425949344371</v>
+        <v>-0.3265573489322655</v>
       </c>
       <c r="J14" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K14" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3443247786049896</v>
+        <v>0.3272297020587949</v>
       </c>
       <c r="M14" t="n">
-        <v>2.746861827707475</v>
+        <v>2.775042346188016</v>
       </c>
       <c r="N14" t="n">
-        <v>12.27261645023423</v>
+        <v>12.62143921682802</v>
       </c>
       <c r="O14" t="n">
-        <v>3.503229431572278</v>
+        <v>3.552666493892723</v>
       </c>
       <c r="P14" t="n">
-        <v>325.5144524973416</v>
+        <v>325.4193534465307</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -27179,28 +27319,28 @@
         <v>0.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3401071124835452</v>
+        <v>-0.3325392802464417</v>
       </c>
       <c r="J15" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K15" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1685421287813501</v>
+        <v>0.1625736733024589</v>
       </c>
       <c r="M15" t="n">
-        <v>4.405342893548832</v>
+        <v>4.426820756922375</v>
       </c>
       <c r="N15" t="n">
-        <v>32.665142095896</v>
+        <v>32.79126420331182</v>
       </c>
       <c r="O15" t="n">
-        <v>5.715342692778448</v>
+        <v>5.726365706389334</v>
       </c>
       <c r="P15" t="n">
-        <v>311.6824393799132</v>
+        <v>311.6023574058615</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -27257,28 +27397,28 @@
         <v>0.1368</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3290413603957809</v>
+        <v>-0.3219809815592681</v>
       </c>
       <c r="J16" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K16" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1969896817033172</v>
+        <v>0.1902027376537945</v>
       </c>
       <c r="M16" t="n">
-        <v>3.918077981287036</v>
+        <v>3.937043433461741</v>
       </c>
       <c r="N16" t="n">
-        <v>25.26387598198838</v>
+        <v>25.40948393902938</v>
       </c>
       <c r="O16" t="n">
-        <v>5.026318332735043</v>
+        <v>5.040782076129594</v>
       </c>
       <c r="P16" t="n">
-        <v>319.8700648203491</v>
+        <v>319.795367719097</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -27335,28 +27475,28 @@
         <v>0.1222</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.371117674735608</v>
+        <v>-0.365617839628847</v>
       </c>
       <c r="J17" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K17" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2093525521666645</v>
+        <v>0.2052033601791843</v>
       </c>
       <c r="M17" t="n">
-        <v>4.264140754210759</v>
+        <v>4.271339979114344</v>
       </c>
       <c r="N17" t="n">
-        <v>29.77482652724945</v>
+        <v>29.80589551894446</v>
       </c>
       <c r="O17" t="n">
-        <v>5.456631426736594</v>
+        <v>5.459477586632668</v>
       </c>
       <c r="P17" t="n">
-        <v>323.4213089747367</v>
+        <v>323.3631371904181</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -27394,7 +27534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R362"/>
+  <dimension ref="A1:R364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60681,6 +60821,190 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>-38.795175762549,174.59165199579962</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>-38.79449837430408,174.59188120074094</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>-38.79380872339124,174.59204076774319</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>-38.79314616771198,174.59235432301935</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>-38.792449387470796,174.59247345640816</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>-38.79175678255102,174.59262963356383</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>-38.79108575189155,174.5929275393316</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>-38.79039799109621,174.5930993465331</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>-38.78971649097323,174.59331015520794</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>-38.789032406295235,174.59350342687955</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>-38.78834884717679,174.59370031860348</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>-38.78769405786349,174.5939407883992</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>-38.78703025124905,174.5941176769474</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>-38.78641747429697,174.59457923956575</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>-38.785732866868685,174.59478873463942</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>-38.78507034415675,174.59507945438813</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:06:20+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>-38.795175762549,174.59165199579962</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>-38.79450394888077,174.5919128748866</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>-38.793813447928585,174.59206761188747</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>-38.79315322478664,174.5923944204062</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>-38.792452846818186,174.5924931117983</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>-38.79176268764207,174.59266580875166</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>-38.79109259993004,174.59297356864792</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-38.790400485849254,174.59311631751487</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>-38.78971950128522,174.59333063333528</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>-38.78903478459257,174.5935196055796</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>-38.788351009250604,174.59371502637478</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>-38.787699177029644,174.59396656276576</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>-38.78703431169569,174.5941331778533</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>-38.786426405216325,174.5946120773004</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>-38.7857464702155,174.59483875191899</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>-38.78508628364393,174.59513806108362</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
